--- a/public/downloads/Jia-ChengAtomistic2021.xlsx
+++ b/public/downloads/Jia-ChengAtomistic2021.xlsx
@@ -8,30 +8,32 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="Allegro-OAM-L" sheetId="3" r:id="rId3"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="4" r:id="rId4"/>
-    <sheet name="CHGNetv0.3.0" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="NequIP-OAM-L" sheetId="12" r:id="rId12"/>
-    <sheet name="ORB-v3" sheetId="13" r:id="rId13"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="17" r:id="rId17"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="18" r:id="rId18"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="Allegro-OAM-L" sheetId="5" r:id="rId5"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="6" r:id="rId6"/>
+    <sheet name="CHGNetv0.3.0" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="NequIP-OAM-L" sheetId="14" r:id="rId14"/>
+    <sheet name="ORB-v3" sheetId="15" r:id="rId15"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="19" r:id="rId19"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="20" r:id="rId20"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="54">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -63,10 +65,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -169,6 +171,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>OCO</t>
@@ -657,10 +680,10 @@
         <v>1</v>
       </c>
       <c r="N3" s="5">
-        <v>2.149100065231323</v>
+        <v>2149.100065231323</v>
       </c>
       <c r="O3" s="4">
-        <v>0.02755256493886312</v>
+        <v>27.55256493886312</v>
       </c>
       <c r="P3" s="5">
         <v>78</v>
@@ -707,10 +730,10 @@
         <v>1</v>
       </c>
       <c r="N4" s="5">
-        <v>3.510280132293701</v>
+        <v>3510.280132293701</v>
       </c>
       <c r="O4" s="4">
-        <v>0.04178904919397263</v>
+        <v>41.78904919397263</v>
       </c>
       <c r="P4" s="5">
         <v>84</v>
@@ -757,10 +780,10 @@
         <v>1</v>
       </c>
       <c r="N5" s="5">
-        <v>5.060381174087524</v>
+        <v>5060.381174087524</v>
       </c>
       <c r="O5" s="4">
-        <v>0.06024263302485148</v>
+        <v>60.24263302485148</v>
       </c>
       <c r="P5" s="5">
         <v>84</v>
@@ -807,10 +830,10 @@
         <v>1</v>
       </c>
       <c r="N6" s="5">
-        <v>7.775439500808716</v>
+        <v>7775.439500808716</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08937286782538754</v>
+        <v>89.37286782538754</v>
       </c>
       <c r="P6" s="5">
         <v>87</v>
@@ -857,10 +880,10 @@
         <v>1</v>
       </c>
       <c r="N7" s="5">
-        <v>24.81553983688354</v>
+        <v>24815.53983688354</v>
       </c>
       <c r="O7" s="4">
-        <v>0.2120986310844747</v>
+        <v>212.0986310844747</v>
       </c>
       <c r="P7" s="5">
         <v>117</v>
@@ -907,10 +930,10 @@
         <v>1</v>
       </c>
       <c r="N8" s="5">
-        <v>2.076080560684204</v>
+        <v>2076.080560684204</v>
       </c>
       <c r="O8" s="4">
-        <v>0.02162583917379379</v>
+        <v>21.62583917379379</v>
       </c>
       <c r="P8" s="5">
         <v>96</v>
@@ -957,10 +980,10 @@
         <v>1</v>
       </c>
       <c r="N9" s="5">
-        <v>3.903732538223267</v>
+        <v>3903.732538223267</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03717840512593587</v>
+        <v>37.17840512593587</v>
       </c>
       <c r="P9" s="5">
         <v>105</v>
@@ -1007,10 +1030,10 @@
         <v>1</v>
       </c>
       <c r="N10" s="5">
-        <v>10.56769609451294</v>
+        <v>10567.69609451294</v>
       </c>
       <c r="O10" s="4">
-        <v>0.1067444049950802</v>
+        <v>106.7444049950802</v>
       </c>
       <c r="P10" s="5">
         <v>99</v>
@@ -1057,10 +1080,10 @@
         <v>1</v>
       </c>
       <c r="N11" s="5">
-        <v>4.27495288848877</v>
+        <v>4274.95288848877</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04913738952285942</v>
+        <v>49.13738952285942</v>
       </c>
       <c r="P11" s="5">
         <v>87</v>
@@ -1107,10 +1130,10 @@
         <v>1</v>
       </c>
       <c r="N12" s="5">
-        <v>2.451154708862305</v>
+        <v>2451.154708862305</v>
       </c>
       <c r="O12" s="4">
-        <v>0.03142506037002955</v>
+        <v>31.42506037002954</v>
       </c>
       <c r="P12" s="5">
         <v>78</v>
@@ -1157,10 +1180,10 @@
         <v>1</v>
       </c>
       <c r="N13" s="5">
-        <v>1.5254807472229</v>
+        <v>1525.4807472229</v>
       </c>
       <c r="O13" s="4">
-        <v>0.02542467912038167</v>
+        <v>25.42467912038167</v>
       </c>
       <c r="P13" s="5">
         <v>60</v>
@@ -1207,10 +1230,10 @@
         <v>1</v>
       </c>
       <c r="N14" s="5">
-        <v>7.129446506500244</v>
+        <v>7129.446506500244</v>
       </c>
       <c r="O14" s="4">
-        <v>0.06989653437745337</v>
+        <v>69.89653437745336</v>
       </c>
       <c r="P14" s="5">
         <v>102</v>
@@ -1257,10 +1280,10 @@
         <v>1</v>
       </c>
       <c r="N15" s="5">
-        <v>27.04251432418823</v>
+        <v>27042.51432418823</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2575477554684594</v>
+        <v>257.5477554684594</v>
       </c>
       <c r="P15" s="5">
         <v>105</v>
@@ -1307,10 +1330,10 @@
         <v>1</v>
       </c>
       <c r="N16" s="5">
-        <v>17.668208360672</v>
+        <v>17668.208360672</v>
       </c>
       <c r="O16" s="4">
-        <v>0.2560609907343768</v>
+        <v>256.0609907343768</v>
       </c>
       <c r="P16" s="5">
         <v>69</v>
@@ -1341,9 +1364,7 @@
       <c r="H17" s="4">
         <v>0.1901306926012296</v>
       </c>
-      <c r="I17" s="4">
-        <v>0</v>
-      </c>
+      <c r="I17" s="4"/>
       <c r="J17" s="4">
         <v>0.3666291188853279</v>
       </c>
@@ -1357,10 +1378,10 @@
         <v>1</v>
       </c>
       <c r="N17" s="5">
-        <v>13.98242402076721</v>
+        <v>13982.42402076721</v>
       </c>
       <c r="O17" s="4">
-        <v>0.09321616013844808</v>
+        <v>93.21616013844807</v>
       </c>
       <c r="P17" s="5">
         <v>150</v>
@@ -1407,10 +1428,10 @@
         <v>1</v>
       </c>
       <c r="N18" s="5">
-        <v>8.824002981185913</v>
+        <v>8824.002981185913</v>
       </c>
       <c r="O18" s="4">
-        <v>0.09488175248587004</v>
+        <v>94.88175248587004</v>
       </c>
       <c r="P18" s="5">
         <v>93</v>
@@ -1438,7 +1459,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1449,9 +1470,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -1485,8 +1512,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1508,25 +1543,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1052801869658424</v>
+        <v>0.7663667219935633</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1052801869658424</v>
+        <v>0.7663667219935633</v>
       </c>
       <c r="D3" s="4">
-        <v>0.06706066164485947</v>
+        <v>0.7836978291775836</v>
       </c>
       <c r="E3" s="4">
-        <v>91.73469387755102</v>
+        <v>91.63265306122449</v>
       </c>
       <c r="F3" s="4">
-        <v>86.97986577181209</v>
+        <v>92.18120805369128</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -1549,9 +1602,25 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7663667219935633</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.7663667219935633</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1562,6 +1631,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1569,7 +1639,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1580,9 +1650,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -1616,8 +1692,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1639,25 +1723,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2203299834481527</v>
+        <v>0.3724053507654617</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2203299834481527</v>
+        <v>0.3724053507654617</v>
       </c>
       <c r="D3" s="4">
-        <v>0.09784555915422288</v>
+        <v>0.1759266901356682</v>
       </c>
       <c r="E3" s="4">
-        <v>92.44897959183673</v>
+        <v>89.89795918367346</v>
       </c>
       <c r="F3" s="4">
-        <v>90.90604026845638</v>
+        <v>86.64429530201342</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -1680,9 +1782,25 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3724053507654617</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3724053507654617</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1693,6 +1811,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1700,7 +1819,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1711,9 +1830,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -1747,8 +1872,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1770,25 +1903,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.650578621482282</v>
+        <v>0.1052801869658424</v>
       </c>
       <c r="C3" s="4">
-        <v>0.650578621482282</v>
+        <v>0.1052801869658424</v>
       </c>
       <c r="D3" s="4">
-        <v>0.629737117378852</v>
+        <v>0.06706066164485947</v>
       </c>
       <c r="E3" s="4">
-        <v>93.06122448979592</v>
+        <v>91.73469387755102</v>
       </c>
       <c r="F3" s="4">
-        <v>91.30872483221476</v>
+        <v>86.97986577181209</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -1811,9 +1962,25 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1052801869658424</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1052801869658424</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1824,6 +1991,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1831,7 +1999,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1842,9 +2010,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -1878,8 +2052,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1901,25 +2083,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.09089813656396473</v>
+        <v>0.2203299834481527</v>
       </c>
       <c r="C3" s="4">
-        <v>0.09089813656396473</v>
+        <v>0.2203299834481527</v>
       </c>
       <c r="D3" s="4">
-        <v>0.01972055915422288</v>
+        <v>0.09784555915422288</v>
       </c>
       <c r="E3" s="4">
-        <v>97.65306122448979</v>
+        <v>92.44897959183673</v>
       </c>
       <c r="F3" s="4">
-        <v>94.53020134228188</v>
+        <v>90.90604026845638</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -1942,9 +2142,25 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2203299834481527</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2203299834481527</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1955,6 +2171,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1962,7 +2179,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1973,9 +2190,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -2009,8 +2232,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2032,25 +2263,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3585258099292332</v>
+        <v>0.650578621482282</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3585258099292332</v>
+        <v>0.650578621482282</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2902054834706291</v>
+        <v>0.629737117378852</v>
       </c>
       <c r="E3" s="4">
-        <v>91.53061224489795</v>
+        <v>93.06122448979592</v>
       </c>
       <c r="F3" s="4">
-        <v>90.16778523489933</v>
+        <v>91.30872483221476</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -2073,9 +2322,25 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.650578621482282</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.650578621482282</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2086,6 +2351,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2093,7 +2359,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2104,9 +2370,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -2140,8 +2412,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2163,25 +2443,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1653225249337993</v>
+        <v>0.09089813656396473</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1653225249337993</v>
+        <v>0.09089813656396473</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2335402917521208</v>
+        <v>0.01972055915422288</v>
       </c>
       <c r="E3" s="4">
-        <v>84.79591836734694</v>
+        <v>97.65306122448979</v>
       </c>
       <c r="F3" s="4">
-        <v>80.30201342281879</v>
+        <v>94.53020134228188</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -2204,9 +2502,25 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.09089813656396473</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.09089813656396473</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2217,6 +2531,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2224,7 +2539,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2235,9 +2550,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -2271,8 +2592,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2294,25 +2623,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>1.196317357197529</v>
+        <v>0.3585258099292332</v>
       </c>
       <c r="C3" s="4">
-        <v>1.196317357197529</v>
+        <v>0.3585258099292332</v>
       </c>
       <c r="D3" s="4">
-        <v>1.196336095367144</v>
+        <v>0.2902054834706291</v>
       </c>
       <c r="E3" s="4">
-        <v>97.55102040816327</v>
+        <v>91.53061224489795</v>
       </c>
       <c r="F3" s="4">
-        <v>96.10738255033557</v>
+        <v>90.16778523489933</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -2335,9 +2682,25 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3585258099292332</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3585258099292332</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2348,6 +2711,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2355,7 +2719,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2366,9 +2730,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -2402,8 +2772,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2425,34 +2803,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1901306926012296</v>
+        <v>0.1653225249337993</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
+        <v>0.1653225249337993</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3666291188853279</v>
+        <v>0.2335402917521208</v>
       </c>
       <c r="E3" s="4">
-        <v>72.24489795918367</v>
+        <v>84.79591836734694</v>
       </c>
       <c r="F3" s="4">
-        <v>60.1006711409396</v>
+        <v>80.30201342281879</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
       </c>
       <c r="H3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2466,9 +2862,25 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1653225249337993</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1653225249337993</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2479,6 +2891,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2486,7 +2899,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2497,9 +2910,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -2533,8 +2952,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2556,25 +2983,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5782253998049782</v>
+        <v>1.196317357197529</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5782253998049782</v>
+        <v>1.196317357197529</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5102033067089451</v>
+        <v>1.196336095367144</v>
       </c>
       <c r="E3" s="4">
-        <v>95.10204081632654</v>
+        <v>97.55102040816327</v>
       </c>
       <c r="F3" s="4">
-        <v>94.02684563758389</v>
+        <v>96.10738255033557</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -2597,9 +3042,25 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.196317357197529</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>1.196317357197529</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2610,12 +3071,1274 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.1901306926012296</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4">
+        <v>0.3666291188853279</v>
+      </c>
+      <c r="E3" s="4">
+        <v>72.24489795918367</v>
+      </c>
+      <c r="F3" s="4">
+        <v>60.1006711409396</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1901306926012296</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>100</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>1.766722806439475</v>
+      </c>
+      <c r="I3" s="4">
+        <v>1.766722806439475</v>
+      </c>
+      <c r="J3" s="4">
+        <v>1.61217674102528</v>
+      </c>
+      <c r="K3" s="4">
+        <v>92.75510204081633</v>
+      </c>
+      <c r="L3" s="4">
+        <v>87.5503355704698</v>
+      </c>
+      <c r="M3" s="5">
+        <v>1</v>
+      </c>
+      <c r="N3" s="5">
+        <v>2149.100065231323</v>
+      </c>
+      <c r="O3" s="4">
+        <v>27.55256493886312</v>
+      </c>
+      <c r="P3" s="5">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>100</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.741129198141607</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.741129198141607</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.6833348322255119</v>
+      </c>
+      <c r="K4" s="4">
+        <v>93.67346938775511</v>
+      </c>
+      <c r="L4" s="4">
+        <v>93.60178970917225</v>
+      </c>
+      <c r="M4" s="5">
+        <v>1</v>
+      </c>
+      <c r="N4" s="5">
+        <v>3510.280132293701</v>
+      </c>
+      <c r="O4" s="4">
+        <v>41.78904919397263</v>
+      </c>
+      <c r="P4" s="5">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>100</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.007854416562508959</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.007854416562508959</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.09349446039061604</v>
+      </c>
+      <c r="K5" s="4">
+        <v>91.42857142857143</v>
+      </c>
+      <c r="L5" s="4">
+        <v>88.15436241610739</v>
+      </c>
+      <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="5">
+        <v>5060.381174087524</v>
+      </c>
+      <c r="O5" s="4">
+        <v>60.24263302485148</v>
+      </c>
+      <c r="P5" s="5">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>100</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.2225328226002716</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.2225328226002716</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.2778363275868401</v>
+      </c>
+      <c r="K6" s="4">
+        <v>91.53061224489795</v>
+      </c>
+      <c r="L6" s="4">
+        <v>91.2751677852349</v>
+      </c>
+      <c r="M6" s="5">
+        <v>1</v>
+      </c>
+      <c r="N6" s="5">
+        <v>7775.439500808716</v>
+      </c>
+      <c r="O6" s="4">
+        <v>89.37286782538754</v>
+      </c>
+      <c r="P6" s="5">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>100</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.209266114743059</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.209266114743059</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.2322678614003166</v>
+      </c>
+      <c r="K7" s="4">
+        <v>92.24489795918367</v>
+      </c>
+      <c r="L7" s="4">
+        <v>88.38926174496645</v>
+      </c>
+      <c r="M7" s="5">
+        <v>1</v>
+      </c>
+      <c r="N7" s="5">
+        <v>24815.53983688354</v>
+      </c>
+      <c r="O7" s="4">
+        <v>212.0986310844747</v>
+      </c>
+      <c r="P7" s="5">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>100</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.7663667219935633</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.7663667219935633</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.7836978291775836</v>
+      </c>
+      <c r="K8" s="4">
+        <v>91.63265306122449</v>
+      </c>
+      <c r="L8" s="4">
+        <v>92.18120805369128</v>
+      </c>
+      <c r="M8" s="5">
+        <v>1</v>
+      </c>
+      <c r="N8" s="5">
+        <v>2076.080560684204</v>
+      </c>
+      <c r="O8" s="4">
+        <v>21.62583917379379</v>
+      </c>
+      <c r="P8" s="5">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>100</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.3724053507654617</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.3724053507654617</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.1759266901356682</v>
+      </c>
+      <c r="K9" s="4">
+        <v>89.89795918367346</v>
+      </c>
+      <c r="L9" s="4">
+        <v>86.64429530201342</v>
+      </c>
+      <c r="M9" s="5">
+        <v>1</v>
+      </c>
+      <c r="N9" s="5">
+        <v>3903.732538223267</v>
+      </c>
+      <c r="O9" s="4">
+        <v>37.17840512593587</v>
+      </c>
+      <c r="P9" s="5">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>100</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.1052801869658424</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.1052801869658424</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.06706066164485947</v>
+      </c>
+      <c r="K10" s="4">
+        <v>91.73469387755102</v>
+      </c>
+      <c r="L10" s="4">
+        <v>86.97986577181209</v>
+      </c>
+      <c r="M10" s="5">
+        <v>1</v>
+      </c>
+      <c r="N10" s="5">
+        <v>10567.69609451294</v>
+      </c>
+      <c r="O10" s="4">
+        <v>106.7444049950802</v>
+      </c>
+      <c r="P10" s="5">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>100</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.2203299834481527</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.2203299834481527</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.09784555915422288</v>
+      </c>
+      <c r="K11" s="4">
+        <v>92.44897959183673</v>
+      </c>
+      <c r="L11" s="4">
+        <v>90.90604026845638</v>
+      </c>
+      <c r="M11" s="5">
+        <v>1</v>
+      </c>
+      <c r="N11" s="5">
+        <v>4274.95288848877</v>
+      </c>
+      <c r="O11" s="4">
+        <v>49.13738952285942</v>
+      </c>
+      <c r="P11" s="5">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>100</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.650578621482282</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.650578621482282</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.629737117378852</v>
+      </c>
+      <c r="K12" s="4">
+        <v>93.06122448979592</v>
+      </c>
+      <c r="L12" s="4">
+        <v>91.30872483221476</v>
+      </c>
+      <c r="M12" s="5">
+        <v>1</v>
+      </c>
+      <c r="N12" s="5">
+        <v>2451.154708862305</v>
+      </c>
+      <c r="O12" s="4">
+        <v>31.42506037002954</v>
+      </c>
+      <c r="P12" s="5">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>100</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.09089813656396473</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.09089813656396473</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.01972055915422288</v>
+      </c>
+      <c r="K13" s="4">
+        <v>97.65306122448979</v>
+      </c>
+      <c r="L13" s="4">
+        <v>94.53020134228188</v>
+      </c>
+      <c r="M13" s="5">
+        <v>1</v>
+      </c>
+      <c r="N13" s="5">
+        <v>1525.4807472229</v>
+      </c>
+      <c r="O13" s="4">
+        <v>25.42467912038167</v>
+      </c>
+      <c r="P13" s="5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>100</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.3585258099292332</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.3585258099292332</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.2902054834706291</v>
+      </c>
+      <c r="K14" s="4">
+        <v>91.53061224489795</v>
+      </c>
+      <c r="L14" s="4">
+        <v>90.16778523489933</v>
+      </c>
+      <c r="M14" s="5">
+        <v>1</v>
+      </c>
+      <c r="N14" s="5">
+        <v>7129.446506500244</v>
+      </c>
+      <c r="O14" s="4">
+        <v>69.89653437745336</v>
+      </c>
+      <c r="P14" s="5">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>100</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.1653225249337993</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.1653225249337993</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.2335402917521208</v>
+      </c>
+      <c r="K15" s="4">
+        <v>84.79591836734694</v>
+      </c>
+      <c r="L15" s="4">
+        <v>80.30201342281879</v>
+      </c>
+      <c r="M15" s="5">
+        <v>1</v>
+      </c>
+      <c r="N15" s="5">
+        <v>27042.51432418823</v>
+      </c>
+      <c r="O15" s="4">
+        <v>257.5477554684594</v>
+      </c>
+      <c r="P15" s="5">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>100</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>1.196317357197529</v>
+      </c>
+      <c r="I16" s="4">
+        <v>1.196317357197529</v>
+      </c>
+      <c r="J16" s="4">
+        <v>1.196336095367144</v>
+      </c>
+      <c r="K16" s="4">
+        <v>97.55102040816327</v>
+      </c>
+      <c r="L16" s="4">
+        <v>96.10738255033557</v>
+      </c>
+      <c r="M16" s="5">
+        <v>1</v>
+      </c>
+      <c r="N16" s="5">
+        <v>17668.208360672</v>
+      </c>
+      <c r="O16" s="4">
+        <v>256.0609907343768</v>
+      </c>
+      <c r="P16" s="5">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3">
+        <v>100</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.1901306926012296</v>
+      </c>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4">
+        <v>0.3666291188853279</v>
+      </c>
+      <c r="K17" s="4">
+        <v>72.24489795918367</v>
+      </c>
+      <c r="L17" s="4">
+        <v>60.1006711409396</v>
+      </c>
+      <c r="M17" s="5">
+        <v>1</v>
+      </c>
+      <c r="N17" s="5">
+        <v>13982.42402076721</v>
+      </c>
+      <c r="O17" s="4">
+        <v>93.21616013844807</v>
+      </c>
+      <c r="P17" s="5">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="25" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="3">
+        <v>100</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0.5782253998049782</v>
+      </c>
+      <c r="I18" s="4">
+        <v>0.5782253998049782</v>
+      </c>
+      <c r="J18" s="4">
+        <v>0.5102033067089451</v>
+      </c>
+      <c r="K18" s="4">
+        <v>95.10204081632654</v>
+      </c>
+      <c r="L18" s="4">
+        <v>94.02684563758389</v>
+      </c>
+      <c r="M18" s="5">
+        <v>1</v>
+      </c>
+      <c r="N18" s="5">
+        <v>8824.002981185913</v>
+      </c>
+      <c r="O18" s="4">
+        <v>94.88175248587004</v>
+      </c>
+      <c r="P18" s="5">
+        <v>93</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.5782253998049782</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.5782253998049782</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.5102033067089451</v>
+      </c>
+      <c r="E3" s="4">
+        <v>95.10204081632654</v>
+      </c>
+      <c r="F3" s="4">
+        <v>94.02684563758389</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5782253998049782</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5782253998049782</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3414,9 +5137,808 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:N18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>1</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>1</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>1</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>1</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>1</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>1</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>1</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="25" customHeight="1">
+      <c r="A18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="5">
+        <v>1</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5">
+        <v>0</v>
+      </c>
+      <c r="H18" s="5">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5">
+        <v>0</v>
+      </c>
+      <c r="J18" s="5">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5">
+        <v>0</v>
+      </c>
+      <c r="L18" s="5">
+        <v>0</v>
+      </c>
+      <c r="M18" s="5">
+        <v>0</v>
+      </c>
+      <c r="N18" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3427,9 +5949,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -3463,8 +5991,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3486,10 +6022,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>1.766722806439475</v>
@@ -3527,9 +6081,25 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.766722806439475</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>1.766722806439475</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3540,14 +6110,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3558,9 +6129,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -3594,8 +6171,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3617,10 +6202,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.741129198141607</v>
@@ -3658,9 +6261,25 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.741129198141607</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.741129198141607</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3671,14 +6290,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3689,9 +6309,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -3725,8 +6351,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3748,10 +6382,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.007854416562508959</v>
@@ -3789,9 +6441,25 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.007854416562508959</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.007854416562508959</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3802,14 +6470,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3820,9 +6489,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -3856,8 +6531,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3879,10 +6562,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.2225328226002716</v>
@@ -3920,9 +6621,25 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2225328226002716</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2225328226002716</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3933,14 +6650,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3951,9 +6669,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -3987,8 +6711,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4010,10 +6742,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B3" s="4">
         <v>0.209266114743059</v>
@@ -4051,9 +6801,25 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.209266114743059</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.209266114743059</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4064,268 +6830,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.7663667219935633</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.7663667219935633</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.7836978291775836</v>
-      </c>
-      <c r="E3" s="4">
-        <v>91.63265306122449</v>
-      </c>
-      <c r="F3" s="4">
-        <v>92.18120805369128</v>
-      </c>
-      <c r="G3" s="5">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.3724053507654617</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.3724053507654617</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.1759266901356682</v>
-      </c>
-      <c r="E3" s="4">
-        <v>89.89795918367346</v>
-      </c>
-      <c r="F3" s="4">
-        <v>86.64429530201342</v>
-      </c>
-      <c r="G3" s="5">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
